--- a/data/trans_orig/P1429-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2007</t>
+          <t>Población con diagnóstico de osteoporosis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246336</t>
+          <t>246449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257454</t>
+          <t>257832</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518250</t>
+          <t>519985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530722</t>
+          <t>530994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4994</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48546</t>
+          <t>48285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>26290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48652</t>
+          <t>51970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488064</t>
+          <t>488081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455403</t>
+          <t>455664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478454</t>
+          <t>478766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948372</t>
+          <t>945054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>971652</t>
+          <t>970734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22323</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>24210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313814</t>
+          <t>314222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313089</t>
+          <t>313141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328226</t>
+          <t>327918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631672</t>
+          <t>630048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>646297</t>
+          <t>645904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22997</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348459</t>
+          <t>347930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362799</t>
+          <t>362646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707111</t>
+          <t>706780</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721100</t>
+          <t>721160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198683</t>
+          <t>199550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199022</t>
+          <t>198831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206690</t>
+          <t>206675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401059</t>
+          <t>400724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409827</t>
+          <t>409858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,47 +2498,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>11724</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>21493</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>11724</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>6114</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>20535</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258091</t>
+          <t>258526</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272204</t>
+          <t>271913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,47 +2611,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>537231</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>527462</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>542652</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>97,86%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>537231</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>528420</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>542841</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>97,86%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>14690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38295</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>605542</t>
+          <t>605480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614023</t>
+          <t>614028</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>604121</t>
+          <t>604181</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>623436</t>
+          <t>623529</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1214951</t>
+          <t>1215276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1236716</t>
+          <t>1235405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40876</t>
+          <t>39554</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51762</t>
+          <t>52433</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49507</t>
+          <t>52016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82828</t>
+          <t>83170</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>702919</t>
+          <t>704241</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724320</t>
+          <t>726474</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>731749</t>
+          <t>731078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>756954</t>
+          <t>757330</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1444478</t>
+          <t>1444136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1477799</t>
+          <t>1475290</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>122035</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>169587</t>
+          <t>169092</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>153714</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>206337</t>
+          <t>207773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3230763</t>
+          <t>3228267</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3253340</t>
+          <t>3251746</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3209610</t>
+          <t>3210105</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3257162</t>
+          <t>3258051</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6449404</t>
+          <t>6447968</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6500167</t>
+          <t>6502027</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2012</t>
+          <t>Población con diagnóstico de osteoporosis en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20942</t>
+          <t>20758</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293735</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266303</t>
+          <t>266487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280931</t>
+          <t>280853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559784</t>
+          <t>558807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574335</t>
+          <t>574001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24491</t>
+          <t>25236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>494022</t>
+          <t>493526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498165</t>
+          <t>497420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>515289</t>
+          <t>514454</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998118</t>
+          <t>998361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1018006</t>
+          <t>1017785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18974</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319004</t>
+          <t>318981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322046</t>
+          <t>321807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335767</t>
+          <t>335935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643992</t>
+          <t>644466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659628</t>
+          <t>659084</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41730</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41550</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347221</t>
+          <t>345412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367666</t>
+          <t>368138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>721383</t>
+          <t>721491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743139</t>
+          <t>742569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204716</t>
+          <t>204634</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215673</t>
+          <t>216355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417029</t>
+          <t>417359</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428247</t>
+          <t>428372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273981</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>265691</t>
+          <t>264549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276013</t>
+          <t>275975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539472</t>
+          <t>538747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549932</t>
+          <t>549973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20879</t>
+          <t>21605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>43817</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>22067</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>45158</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656280</t>
+          <t>656806</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>649016</t>
+          <t>650036</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>672974</t>
+          <t>672248</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312023</t>
+          <t>1311483</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1333922</t>
+          <t>1334574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20678</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>43498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21290</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44717</t>
+          <t>43809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772154</t>
+          <t>772820</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>778579</t>
+          <t>779080</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>801900</t>
+          <t>802559</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1556959</t>
+          <t>1557867</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1580386</t>
+          <t>1581266</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120743</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>169238</t>
+          <t>170426</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>125074</t>
+          <t>123147</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>175682</t>
+          <t>174630</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3410313</t>
+          <t>3410664</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3423699</t>
+          <t>3423719</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3384752</t>
+          <t>3383564</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3433247</t>
+          <t>3434752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6804084</t>
+          <t>6805136</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6854692</t>
+          <t>6856619</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2016</t>
+          <t>Población con diagnóstico de osteoporosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>22448</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289647</t>
+          <t>289727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267147</t>
+          <t>267207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281788</t>
+          <t>282358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>559321</t>
+          <t>560016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574836</t>
+          <t>574898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>29867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>498869</t>
+          <t>498384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495031</t>
+          <t>494810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>512796</t>
+          <t>513364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>996447</t>
+          <t>995792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014750</t>
+          <t>1014658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,67 +8080,67 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14334</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>5261</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13127</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,49 +8193,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>331048</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>321975</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>334394</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,74%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>331048</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>323182</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>335059</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>663</t>
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640781</t>
+          <t>640176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653074</t>
+          <t>653629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38052</t>
+          <t>37270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>17543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>40278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363661</t>
+          <t>363914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349231</t>
+          <t>350013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371117</t>
+          <t>372110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>716537</t>
+          <t>716969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>740143</t>
+          <t>739704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -8751,97 +8751,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2161</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7654</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2161</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7393</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>7662</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>7444</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211194</t>
+          <t>210933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422364</t>
+          <t>422146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>8347</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17123</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254074</t>
+          <t>254776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259909</t>
+          <t>260009</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271082</t>
+          <t>270175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519115</t>
+          <t>520290</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532182</t>
+          <t>532865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44436</t>
+          <t>45693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>26475</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52236</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645377</t>
+          <t>645149</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654747</t>
+          <t>654538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>646858</t>
+          <t>645601</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>670178</t>
+          <t>669089</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1295616</t>
+          <t>1296094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321248</t>
+          <t>1321377</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13169</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31898</t>
+          <t>32823</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>14184</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33872</t>
+          <t>33418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>773260</t>
+          <t>773404</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>794269</t>
+          <t>793344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>812998</t>
+          <t>813496</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1570878</t>
+          <t>1571332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590508</t>
+          <t>1590566</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100609</t>
+          <t>101099</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150165</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>111233</t>
+          <t>112228</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159405</t>
+          <t>159314</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3374435</t>
+          <t>3374298</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3388129</t>
+          <t>3388346</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3394377</t>
+          <t>3396560</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3443933</t>
+          <t>3443443</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6779487</t>
+          <t>6779578</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6827659</t>
+          <t>6826664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de osteoporosis en 2023</t>
+          <t>Población con diagnóstico de osteoporosis en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303975</t>
+          <t>304784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310729</t>
+          <t>310749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274630</t>
+          <t>274833</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283726</t>
+          <t>283600</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582621</t>
+          <t>582959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593424</t>
+          <t>593209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -11050,7 +11050,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>513000</t>
+          <t>513047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484320</t>
+          <t>484354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498137</t>
+          <t>498065</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1001299</t>
+          <t>1001326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1015008</t>
+          <t>1014561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11248,7 +11248,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>12173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>310775</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326618</t>
+          <t>326737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337895</t>
+          <t>338220</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639939</t>
+          <t>639730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652458</t>
+          <t>652378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>20234</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46327</t>
+          <t>44657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27503</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>54731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>290131</t>
+          <t>292323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310036</t>
+          <t>309782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429391</t>
+          <t>431061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>456303</t>
+          <t>455686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>732392</t>
+          <t>733543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760771</t>
+          <t>760557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174596</t>
+          <t>174649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178291</t>
+          <t>178306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193352</t>
+          <t>193561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201155</t>
+          <t>201032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370454</t>
+          <t>370749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378918</t>
+          <t>378693</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>14667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27578</t>
+          <t>27653</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260292</t>
+          <t>259693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267318</t>
+          <t>267024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234775</t>
+          <t>234625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245489</t>
+          <t>245154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497928</t>
+          <t>497853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510428</t>
+          <t>510839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50015</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51583</t>
+          <t>51306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609885</t>
+          <t>609109</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617866</t>
+          <t>617735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>794611</t>
+          <t>793243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>828804</t>
+          <t>828346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1412430</t>
+          <t>1412707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1439751</t>
+          <t>1440756</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>32493</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>17752</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41189</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>917314</t>
+          <t>916785</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>927088</t>
+          <t>927194</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>681052</t>
+          <t>681712</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695475</t>
+          <t>695933</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1601737</t>
+          <t>1601167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1624785</t>
+          <t>1625174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19140</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44762</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>130962</t>
+          <t>133684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>183702</t>
+          <t>182674</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>162971</t>
+          <t>160015</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>215511</t>
+          <t>212931</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3408021</t>
+          <t>3407087</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3433643</t>
+          <t>3433058</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3463638</t>
+          <t>3464666</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3516378</t>
+          <t>3513656</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,17 +13624,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6911350</t>
+          <t>6911351</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6884612</t>
+          <t>6887193</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6937152</t>
+          <t>6940109</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7100123</t>
+          <t>7100124</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P1429-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1429-Provincia-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246449</t>
+          <t>246762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257832</t>
+          <t>257935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519985</t>
+          <t>518930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530994</t>
+          <t>530505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25183</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48285</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51970</t>
+          <t>50299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488081</t>
+          <t>488111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455664</t>
+          <t>456855</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478766</t>
+          <t>479847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>945054</t>
+          <t>946725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970734</t>
+          <t>971086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>22802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314222</t>
+          <t>314352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313141</t>
+          <t>313092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327918</t>
+          <t>327798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>630048</t>
+          <t>631456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645904</t>
+          <t>645954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23526</t>
+          <t>24639</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347930</t>
+          <t>346817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362646</t>
+          <t>362244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706780</t>
+          <t>706623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721160</t>
+          <t>721246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>9911</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199550</t>
+          <t>200012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198831</t>
+          <t>197757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206675</t>
+          <t>206686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>400724</t>
+          <t>401350</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409858</t>
+          <t>409984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>20092</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258526</t>
+          <t>258072</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271913</t>
+          <t>271674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527462</t>
+          <t>528863</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542652</t>
+          <t>542837</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>8637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14690</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34038</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37970</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>605480</t>
+          <t>606390</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614028</t>
+          <t>614072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>604181</t>
+          <t>605756</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>623529</t>
+          <t>623908</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1215276</t>
+          <t>1215364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1235405</t>
+          <t>1235112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39554</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>51545</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>50250</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83170</t>
+          <t>83120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>704241</t>
+          <t>705104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726474</t>
+          <t>725795</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>731078</t>
+          <t>731966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>757330</t>
+          <t>756846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1444136</t>
+          <t>1444186</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1475290</t>
+          <t>1477056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>46684</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121146</t>
+          <t>121541</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>169092</t>
+          <t>169876</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>153714</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>207773</t>
+          <t>206130</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3228267</t>
+          <t>3229859</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3251746</t>
+          <t>3252419</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3210105</t>
+          <t>3209321</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3258051</t>
+          <t>3257656</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6447968</t>
+          <t>6449611</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6502027</t>
+          <t>6500686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266487</t>
+          <t>265616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280853</t>
+          <t>280868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558807</t>
+          <t>558469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574001</t>
+          <t>574778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12001</t>
+          <t>10811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29823</t>
+          <t>32192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493526</t>
+          <t>494716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497420</t>
+          <t>498141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>514454</t>
+          <t>515299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>998361</t>
+          <t>995992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1017785</t>
+          <t>1017733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318981</t>
+          <t>318967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321807</t>
+          <t>321903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335935</t>
+          <t>336046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644466</t>
+          <t>644484</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659084</t>
+          <t>659696</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20813</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43539</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41442</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345412</t>
+          <t>346109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368138</t>
+          <t>368558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>721491</t>
+          <t>721242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>742569</t>
+          <t>742261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14957</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204634</t>
+          <t>203816</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216355</t>
+          <t>215641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417359</t>
+          <t>417206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>428372</t>
+          <t>428304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>12504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264549</t>
+          <t>265592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275975</t>
+          <t>275910</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538747</t>
+          <t>539174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549973</t>
+          <t>549963</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43817</t>
+          <t>44387</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>46334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656806</t>
+          <t>656364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>650036</t>
+          <t>649466</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>672248</t>
+          <t>672644</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1311483</t>
+          <t>1310307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1334574</t>
+          <t>1333682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20019</t>
+          <t>19750</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43498</t>
+          <t>41570</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43809</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772820</t>
+          <t>772757</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>779080</t>
+          <t>781008</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>802559</t>
+          <t>802828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1557867</t>
+          <t>1557192</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1581266</t>
+          <t>1579733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>119540</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>170426</t>
+          <t>170831</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>123147</t>
+          <t>124345</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174630</t>
+          <t>175054</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3410664</t>
+          <t>3409462</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3423719</t>
+          <t>3423723</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3383564</t>
+          <t>3383159</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3434752</t>
+          <t>3434450</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6805136</t>
+          <t>6804712</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6856619</t>
+          <t>6855421</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>289727</t>
+          <t>288492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267207</t>
+          <t>267009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282358</t>
+          <t>281434</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560016</t>
+          <t>560776</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574898</t>
+          <t>575265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>28232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29867</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>498384</t>
+          <t>498851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494810</t>
+          <t>494852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>513364</t>
+          <t>512477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995792</t>
+          <t>994949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014658</t>
+          <t>1014952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321975</t>
+          <t>322586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334394</t>
+          <t>335049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640176</t>
+          <t>640485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653629</t>
+          <t>653062</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37270</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40278</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363914</t>
+          <t>362580</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350013</t>
+          <t>349454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>372110</t>
+          <t>371901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>716969</t>
+          <t>717437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>739704</t>
+          <t>740609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210933</t>
+          <t>211017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422146</t>
+          <t>423230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254776</t>
+          <t>255085</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260009</t>
+          <t>259871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270175</t>
+          <t>270901</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>520290</t>
+          <t>519885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532865</t>
+          <t>532232</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11535</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45693</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>25808</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645149</t>
+          <t>645023</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654538</t>
+          <t>654738</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>645601</t>
+          <t>647235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>669089</t>
+          <t>670131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1296094</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1321377</t>
+          <t>1322044</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>33627</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33418</t>
+          <t>33189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>773404</t>
+          <t>773988</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>793344</t>
+          <t>792540</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>813496</t>
+          <t>812055</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1571332</t>
+          <t>1571561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590566</t>
+          <t>1591294</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>101099</t>
+          <t>100010</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>147982</t>
+          <t>146917</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>112228</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159314</t>
+          <t>158527</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3374298</t>
+          <t>3373801</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3388346</t>
+          <t>3387783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3396560</t>
+          <t>3397625</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3443443</t>
+          <t>3444532</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6779578</t>
+          <t>6780365</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6826664</t>
+          <t>6827373</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308906</t>
+          <t>316503</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304784</t>
+          <t>312737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310749</t>
+          <t>318194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>280003</t>
+          <t>306364</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274833</t>
+          <t>301348</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>283600</t>
+          <t>310168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>588908</t>
+          <t>622866</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>582959</t>
+          <t>616927</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593209</t>
+          <t>627052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>941</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>25547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17654</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -11153,27 +11153,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>528719</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>513047</t>
+          <t>524759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>492578</t>
+          <t>522834</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484354</t>
+          <t>514754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498065</t>
+          <t>528589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,17 +11223,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1009107</t>
+          <t>1051552</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1001326</t>
+          <t>1043872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1014561</t>
+          <t>1057783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>509368</t>
+          <t>540301</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>509368</t>
+          <t>540301</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>509368</t>
+          <t>540301</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1026761</t>
+          <t>1069960</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1026761</t>
+          <t>1069960</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1026761</t>
+          <t>1069960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>901</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -11393,12 +11393,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>16713</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -11496,27 +11496,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>314490</t>
+          <t>314480</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310775</t>
+          <t>310813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315423</t>
+          <t>315381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>332684</t>
+          <t>339668</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326737</t>
+          <t>332754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338220</t>
+          <t>344819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>647175</t>
+          <t>654149</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639730</t>
+          <t>646775</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652378</t>
+          <t>659373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315423</t>
+          <t>315381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315423</t>
+          <t>315381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315423</t>
+          <t>315381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664551</t>
+          <t>671763</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664551</t>
+          <t>671763</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664551</t>
+          <t>671763</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>33956</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>45923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>39745</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54731</t>
+          <t>55265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>304829</t>
+          <t>365321</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292323</t>
+          <t>353490</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309782</t>
+          <t>370030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>443701</t>
+          <t>388005</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>431061</t>
+          <t>376038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>455686</t>
+          <t>395169</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>748529</t>
+          <t>753327</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>733543</t>
+          <t>739842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>760557</t>
+          <t>764325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>469</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177241</t>
+          <t>204063</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>174649</t>
+          <t>201333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178306</t>
+          <t>205196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>197859</t>
+          <t>216069</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193561</t>
+          <t>211855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201032</t>
+          <t>219683</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>375100</t>
+          <t>420132</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370749</t>
+          <t>415183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>378693</t>
+          <t>423689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27653</t>
+          <t>27740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>264693</t>
+          <t>265916</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259693</t>
+          <t>261965</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267024</t>
+          <t>268393</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>240540</t>
+          <t>246911</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234625</t>
+          <t>241339</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245154</t>
+          <t>251763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>505233</t>
+          <t>512827</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497853</t>
+          <t>505569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510839</t>
+          <t>518357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269119</t>
+          <t>270209</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269119</t>
+          <t>270209</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269119</t>
+          <t>270209</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525506</t>
+          <t>533309</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525506</t>
+          <t>533309</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525506</t>
+          <t>533309</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>43240</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16280</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>55312</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>48340</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23257</t>
+          <t>38634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51306</t>
+          <t>61946</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>614887</t>
+          <t>709222</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>609109</t>
+          <t>702820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>617735</t>
+          <t>712519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>810405</t>
+          <t>722669</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>793243</t>
+          <t>710597</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>828346</t>
+          <t>731606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1425293</t>
+          <t>1431890</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1412707</t>
+          <t>1418284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1440756</t>
+          <t>1441596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>619386</t>
+          <t>714322</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619386</t>
+          <t>714322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>619386</t>
+          <t>714322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>844626</t>
+          <t>765909</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>844626</t>
+          <t>765909</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>844626</t>
+          <t>765909</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1464013</t>
+          <t>1480230</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1464013</t>
+          <t>1480230</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1464013</t>
+          <t>1480230</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>37033</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>35261</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17752</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41759</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>922891</t>
+          <t>791570</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>916785</t>
+          <t>786008</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>927194</t>
+          <t>795225</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>689114</t>
+          <t>800511</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>681712</t>
+          <t>792237</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695933</t>
+          <t>808352</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1612005</t>
+          <t>1592081</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1601167</t>
+          <t>1581508</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1625174</t>
+          <t>1600999</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714205</t>
+          <t>829270</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714205</t>
+          <t>829270</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714205</t>
+          <t>829270</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1642926</t>
+          <t>1627342</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1642926</t>
+          <t>1627342</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1642926</t>
+          <t>1627342</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,22 +13441,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>160456</t>
+          <t>176773</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>133684</t>
+          <t>156533</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182674</t>
+          <t>197422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>188773</t>
+          <t>206281</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>160015</t>
+          <t>183894</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>212931</t>
+          <t>231336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -13554,27 +13554,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3424466</t>
+          <t>3495792</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3407087</t>
+          <t>3482002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3433058</t>
+          <t>3505280</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3486884</t>
+          <t>3543033</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3464666</t>
+          <t>3522384</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3513656</t>
+          <t>3563273</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6911351</t>
+          <t>7038824</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6887193</t>
+          <t>7013769</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6940109</t>
+          <t>7061211</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3452783</t>
+          <t>3525299</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3647340</t>
+          <t>3719806</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7100124</t>
+          <t>7245105</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
